--- a/erp-server/erp-server-wms/src/main/resources/excel/StocktakingTaskTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/StocktakingTaskTemplate.xlsx
@@ -18,10 +18,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>盘点计划单号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>仓库</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -35,6 +31,10 @@
   </si>
   <si>
     <t>盘点数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盘点任务单号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -396,19 +396,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
